--- a/Folha_de_Presencas_Introducao_a_Programacao_2026-27_24set2026.xlsx
+++ b/Folha_de_Presencas_Introducao_a_Programacao_2026-27_24set2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="58">
   <si>
     <t>REGISTO DE PRESENÇAS</t>
   </si>
@@ -2404,7 +2404,9 @@
       <c r="G10" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
@@ -2518,7 +2520,9 @@
       <c r="G12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I12" s="27"/>
       <c r="J12" s="27"/>
       <c r="K12" s="27"/>
@@ -2683,7 +2687,9 @@
       <c r="G15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I15" s="27"/>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
@@ -2742,7 +2748,9 @@
       <c r="G16" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I16" s="27"/>
       <c r="J16" s="27"/>
       <c r="K16" s="27"/>
@@ -2801,7 +2809,9 @@
       <c r="G17" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I17" s="27"/>
       <c r="J17" s="27"/>
       <c r="K17" s="27"/>
@@ -2860,7 +2870,9 @@
       <c r="G18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I18" s="27"/>
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
@@ -3031,7 +3043,9 @@
       <c r="G21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="27"/>
+      <c r="H21" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I21" s="27"/>
       <c r="J21" s="27"/>
       <c r="K21" s="27"/>
@@ -3090,7 +3104,9 @@
       <c r="G22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I22" s="27"/>
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
@@ -3206,7 +3222,9 @@
       <c r="G24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="27"/>
+      <c r="H24" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I24" s="27"/>
       <c r="J24" s="27"/>
       <c r="K24" s="27"/>
@@ -3265,7 +3283,9 @@
       <c r="G25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="27"/>
+      <c r="H25" s="27" t="s">
+        <v>19</v>
+      </c>
       <c r="I25" s="27"/>
       <c r="J25" s="27"/>
       <c r="K25" s="27"/>
@@ -3324,7 +3344,9 @@
       <c r="G26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="36"/>
+      <c r="H26" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="I26" s="36"/>
       <c r="J26" s="36"/>
       <c r="K26" s="36"/>
@@ -3424,7 +3446,7 @@
       </c>
       <c r="H28" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I28" s="42">
         <f t="shared" si="3"/>
